--- a/NBFC-MF/Borrowers/Salam_Bidyalaxmi_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Salam_Bidyalaxmi_Daily.xlsx
@@ -4741,77 +4741,81 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="19"/>
-      <c r="B13" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A13" s="19">
+        <v>46279</v>
+      </c>
+      <c r="B13" s="24">
+        <f t="shared" si="3"/>
+        <v>12</v>
       </c>
       <c r="C13" s="20"/>
-      <c r="D13" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E13" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F13" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G13" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H13" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E13" s="21">
+        <f t="shared" si="1"/>
+        <v>52.140422070995719</v>
+      </c>
+      <c r="F13" s="21">
+        <f t="shared" si="5"/>
+        <v>147.85957792900427</v>
+      </c>
+      <c r="G13" s="21">
+        <f t="shared" si="4"/>
+        <v>8284.4448324758487</v>
+      </c>
+      <c r="H13" s="21">
+        <f t="shared" si="2"/>
+        <v>1715.5551675241513</v>
       </c>
       <c r="J13" s="26" t="s">
         <v>22</v>
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>9800</v>
+        <v>9400</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A14" s="2">
+        <v>46280</v>
+      </c>
+      <c r="B14" s="23">
+        <f t="shared" si="3"/>
+        <v>13</v>
       </c>
       <c r="C14" s="3"/>
-      <c r="D14" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E14" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F14" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G14" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H14" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D14" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E14" s="4">
+        <f t="shared" si="1"/>
+        <v>51.226145210812085</v>
+      </c>
+      <c r="F14" s="4">
+        <f t="shared" si="5"/>
+        <v>148.77385478918791</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="4"/>
+        <v>8135.670977686661</v>
+      </c>
+      <c r="H14" s="4">
+        <f t="shared" si="2"/>
+        <v>1864.329022313339</v>
       </c>
       <c r="J14" s="11" t="s">
         <v>23</v>
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>8432.3044104048531</v>
+        <v>8135.670977686661</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4846,7 +4850,7 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1567.6955895951469</v>
+        <v>1864.329022313339</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Salam_Bidyalaxmi_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Salam_Bidyalaxmi_Daily.xlsx
@@ -4741,7 +4741,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>9400</v>
+        <v>9200</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -4815,42 +4815,44 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>8135.670977686661</v>
+        <v>7985.9771926857193</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="19"/>
-      <c r="B15" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A15" s="19">
+        <v>46293</v>
+      </c>
+      <c r="B15" s="24">
+        <f t="shared" si="3"/>
+        <v>14</v>
       </c>
       <c r="C15" s="20"/>
-      <c r="D15" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E15" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F15" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G15" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H15" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E15" s="21">
+        <f t="shared" si="1"/>
+        <v>50.306214999058163</v>
+      </c>
+      <c r="F15" s="21">
+        <f t="shared" si="5"/>
+        <v>149.69378500094183</v>
+      </c>
+      <c r="G15" s="21">
+        <f t="shared" si="4"/>
+        <v>7985.9771926857193</v>
+      </c>
+      <c r="H15" s="21">
+        <f t="shared" si="2"/>
+        <v>2014.0228073142807</v>
       </c>
       <c r="J15" s="13" t="s">
         <v>6</v>
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1864.329022313339</v>
+        <v>2014.0228073142807</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Salam_Bidyalaxmi_Daily.xlsx
+++ b/NBFC-MF/Borrowers/Salam_Bidyalaxmi_Daily.xlsx
@@ -4741,7 +4741,7 @@
       </c>
       <c r="K12" s="10">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="K13" s="12">
         <f>(K10*K9)-K9*K12</f>
-        <v>9200</v>
+        <v>8600</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="K14" s="12">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>7985.9771926857193</v>
+        <v>7531.3191972432815</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -4852,35 +4852,37 @@
       </c>
       <c r="K15" s="14">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>2014.0228073142807</v>
+        <v>2468.6808027567185</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A16" s="2">
+        <v>46299</v>
+      </c>
+      <c r="B16" s="23">
+        <f t="shared" si="3"/>
+        <v>15</v>
       </c>
       <c r="C16" s="3"/>
-      <c r="D16" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E16" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F16" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G16" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H16" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D16" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E16" s="4">
+        <f t="shared" si="1"/>
+        <v>49.380596478725444</v>
+      </c>
+      <c r="F16" s="4">
+        <f t="shared" si="5"/>
+        <v>150.61940352127456</v>
+      </c>
+      <c r="G16" s="4">
+        <f t="shared" si="4"/>
+        <v>7835.3577891644445</v>
+      </c>
+      <c r="H16" s="4">
+        <f t="shared" si="2"/>
+        <v>2164.6422108355555</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>18</v>
@@ -4891,31 +4893,33 @@
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A17" s="19"/>
-      <c r="B17" s="24" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A17" s="19">
+        <v>46301</v>
+      </c>
+      <c r="B17" s="24">
+        <f t="shared" si="3"/>
+        <v>16</v>
       </c>
       <c r="C17" s="20"/>
-      <c r="D17" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E17" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F17" s="21" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G17" s="21" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H17" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D17" s="21">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E17" s="21">
+        <f t="shared" si="1"/>
+        <v>48.449254476651802</v>
+      </c>
+      <c r="F17" s="21">
+        <f t="shared" si="5"/>
+        <v>151.55074552334821</v>
+      </c>
+      <c r="G17" s="21">
+        <f t="shared" si="4"/>
+        <v>7683.8070436410962</v>
+      </c>
+      <c r="H17" s="21">
+        <f t="shared" si="2"/>
+        <v>2316.1929563589038</v>
       </c>
       <c r="J17" s="17" t="s">
         <v>19</v>
@@ -4926,31 +4930,33 @@
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="23" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+      <c r="A18" s="2">
+        <v>46305</v>
+      </c>
+      <c r="B18" s="23">
+        <f t="shared" si="3"/>
+        <v>17</v>
       </c>
       <c r="C18" s="3"/>
-      <c r="D18" s="4" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E18" s="4" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F18" s="4" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="G18" s="4" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="H18" s="4" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+      <c r="D18" s="4">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="E18" s="4">
+        <f t="shared" si="1"/>
+        <v>47.512153602184902</v>
+      </c>
+      <c r="F18" s="4">
+        <f t="shared" si="5"/>
+        <v>152.4878463978151</v>
+      </c>
+      <c r="G18" s="4">
+        <f t="shared" si="4"/>
+        <v>7531.3191972432815</v>
+      </c>
+      <c r="H18" s="4">
+        <f t="shared" si="2"/>
+        <v>2468.6808027567185</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
